--- a/output/2026-10-06_17_Croazia_Grad_Zagreb_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-06_17_Croazia_Grad_Zagreb_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,6 @@
           <t>Trgostal-Lubenjak d.o.o.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Grad Zagreb</t>
@@ -517,11 +516,9 @@
           <t>Macchine e utensili per lavorazione metalli (taglio laser/plasma/acqua piegatrici)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Attiva dal 1978 oltre 300.000 referenze di utensili 900+ marchi distribuiti; verificato via ricerca web (automa.net)</t>
+          <t>Attiva dal 1978 oltre 300.000 referenze di utensili 900+ marchi distribuiti; verificato via ricerca web (automa.net) [DUPLICATO — vedi anche: 2026-09-07_23_Croazia_Zagrebacka_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -536,7 +533,6 @@
           <t>Lorsel Strojevi d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Zagrebačka županija (Zaprešić - area metropolitana Zagabria)</t>
@@ -547,8 +543,6 @@
           <t>Macchine e utensili per lavorazione lamiera</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Fondata 2011 rappresentante marchi esteri per taglio/piegatura lamiera espone a fiere internazionali (Blechexpo); verificato via ricerca web</t>
@@ -608,7 +602,6 @@
           <t>Boltar d.o.o.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Grad Zagreb</t>
@@ -730,7 +723,6 @@
           <t>Aqua Velebita d.o.o.</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Grad Zagreb</t>
@@ -741,8 +733,6 @@
           <t>Ingrosso utensili manuali e macchine utensili (NACE G46620)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Confermata su registro imprese (fininfo.hr) indirizzo Lovinac 102 Zagreb</t>
@@ -802,7 +792,6 @@
           <t>Würth Hrvatska d.o.o.</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Grad Zagreb</t>
@@ -813,8 +802,6 @@
           <t>Utensili fissaggi e materiale tecnico-industriale</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Filiale croata del gruppo Würth leader mondiale sede Franje Lučića 32 Zagreb confermata via registro imprese/LEI</t>
@@ -859,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Distributore autorizzato dal 1992 incluso per rilevanza nel mercato metropolitano di Zagabria pur essendo fuori Grad Zagreb</t>
+          <t>Distributore autorizzato dal 1992 incluso per rilevanza nel mercato metropolitano di Zagabria pur essendo fuori Grad Zagreb [DUPLICATO — vedi anche: 2026-09-08_06_Croazia_Krapinsko-zagorska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -874,7 +861,6 @@
           <t>Jedinstvo Pno</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Grad Zagreb</t>
@@ -885,8 +871,6 @@
           <t>Rivendita macchinari per lavorazione metalli di precisione (centri di lavoro usati marchi +GF+ DMG SIGMA)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Verificato come rivenditore/dealer tramite piattaforma Machineseeker referente Antonio Radovic indirizzo Samoborska cesta 145 Zagreb</t>

--- a/output/2026-10-06_17_Croazia_Grad_Zagreb_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-06_17_Croazia_Grad_Zagreb_Utensilerie_e_Macchine_Utensili.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
